--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T03:12:48+00:00</t>
+    <t>2026-03-18T09:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:54:13+00:00</t>
+    <t>2026-03-23T13:24:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:24:52+00:00</t>
+    <t>2026-03-25T02:48:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T02:48:03+00:00</t>
+    <t>2026-03-25T03:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:05:28+00:00</t>
+    <t>2026-03-25T03:10:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:10:05+00:00</t>
+    <t>2026-03-25T03:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:15:34+00:00</t>
+    <t>2026-03-25T03:26:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="248">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:26:10+00:00</t>
+    <t>2026-03-25T03:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -507,9 +507,6 @@
   </si>
   <si>
     <t>Depending on the context of use, the code that was actually selected by the user (prescriber, dispenser, etc.) will have the coding.userSelected set to true.  As described in the coding datatype: "A coding may be marked as a "userSelected" if a user selected the particular coded value in a user interface (e.g. the user selects an item in a pick-list). If a user selected coding exists, it is the preferred choice for performing translations etc. Other codes can only be literal translations to alternative code systems, or codes at a lower level of granularity (e.g. a generic code for a vendor-specific primary one).</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>http://doh.gov.ph/fhir/ph-core/ValueSet/drugs-vs</t>
@@ -2469,11 +2466,11 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -2506,24 +2503,24 @@
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>162</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2549,13 +2546,13 @@
         <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2581,14 +2578,14 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>169</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
       </c>
@@ -2605,7 +2602,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2623,7 +2620,7 @@
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -2634,10 +2631,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2660,13 +2657,13 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2717,7 +2714,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -2732,24 +2729,24 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>178</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2775,13 +2772,13 @@
         <v>153</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2807,14 +2804,14 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
       </c>
@@ -2831,7 +2828,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -2846,24 +2843,24 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>188</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2886,13 +2883,13 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2943,7 +2940,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2961,7 +2958,7 @@
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -2972,10 +2969,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2998,16 +2995,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3057,7 +3054,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3075,7 +3072,7 @@
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3086,10 +3083,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3112,13 +3109,13 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3169,7 +3166,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3187,7 +3184,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3198,10 +3195,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3230,7 +3227,7 @@
         <v>135</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>137</v>
@@ -3283,7 +3280,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3301,7 +3298,7 @@
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -3312,14 +3309,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3341,10 +3338,10 @@
         <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>137</v>
@@ -3399,7 +3396,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3428,10 +3425,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3454,17 +3451,17 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -3513,7 +3510,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>88</v>
@@ -3528,24 +3525,24 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3568,17 +3565,17 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -3627,7 +3624,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3645,7 +3642,7 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -3656,10 +3653,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3682,13 +3679,13 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3739,7 +3736,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3754,24 +3751,24 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>231</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3794,13 +3791,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3851,7 +3848,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3866,10 +3863,10 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -3880,10 +3877,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3906,13 +3903,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3963,7 +3960,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3981,7 +3978,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -3992,10 +3989,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4024,7 +4021,7 @@
         <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>137</v>
@@ -4077,7 +4074,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4095,7 +4092,7 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4106,14 +4103,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4135,10 +4132,10 @@
         <v>134</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>137</v>
@@ -4193,7 +4190,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4222,10 +4219,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4248,13 +4245,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4305,7 +4302,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4320,7 +4317,7 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>150</v>
@@ -4329,15 +4326,15 @@
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4360,13 +4357,13 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4417,7 +4414,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4432,16 +4429,16 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:31:02+00:00</t>
+    <t>2026-03-25T03:34:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:34:45+00:00</t>
+    <t>2026-03-25T03:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:48:45+00:00</t>
+    <t>2026-03-25T03:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$63</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="345">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:54:03+00:00</t>
+    <t>2026-04-01T03:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -528,6 +531,217 @@
     <t>RXO-1.1-Requested Give Code.code / RXE-2.1-Give Code.code / RXD-2.1-Dispense/Give Code.code / RXG-4.1-Give Code.code /RXA-5.1-Administered Code.code / RXC-2.1 Component Code</t>
   </si>
   <si>
+    <t>Medication.code.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Medication.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Medication.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.id</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Medication.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Medication.status</t>
   </si>
   <si>
@@ -609,6 +823,39 @@
     <t>RXO-5-Requested Dosage Form / RXE-6-Give Dosage Form / RXD-6-Actual Dosage Form / RXG-8-Give Dosage Form / RXA-8-Administered Dosage Form</t>
   </si>
   <si>
+    <t>Medication.form.id</t>
+  </si>
+  <si>
+    <t>Medication.form.extension</t>
+  </si>
+  <si>
+    <t>Medication.form.coding</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.id</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.system</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.version</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.code</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.display</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.form.text</t>
+  </si>
+  <si>
     <t>Medication.amount</t>
   </si>
   <si>
@@ -647,29 +894,7 @@
     <t>Medication.ingredient.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Medication.ingredient.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Medication.ingredient.modifierExtension</t>
@@ -705,17 +930,89 @@
     <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>.player</t>
   </si>
   <si>
     <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
   </si>
   <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.system</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.system</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].text</t>
+  </si>
+  <si>
     <t>Medication.ingredient.isActive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
   </si>
   <si>
     <t>Active ingredient indicator</t>
@@ -924,6 +1221,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1099,12 +1411,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN29"/>
+  <dimension ref="A1:AN63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.79296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="58.71875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.75" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1130,7 +1442,7 @@
     <col min="26" max="26" width="45.22265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1265,7 +1577,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1377,7 +1689,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1491,7 +1803,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1603,7 +1915,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -1717,7 +2029,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -1831,7 +2143,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -1945,7 +2257,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2059,7 +2371,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2173,7 +2485,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2289,7 +2601,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2422,7 +2734,7 @@
         <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>78</v>
@@ -2515,7 +2827,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>162</v>
       </c>
@@ -2537,23 +2849,21 @@
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N13" t="s" s="2">
         <v>165</v>
       </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>78</v>
@@ -2578,74 +2888,74 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="AG13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
+      <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AA13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>78</v>
@@ -2654,18 +2964,20 @@
         <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -2702,51 +3014,51 @@
         <v>78</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2757,30 +3069,32 @@
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
       </c>
@@ -2804,13 +3118,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -2828,13 +3142,13 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>78</v>
@@ -2843,24 +3157,24 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2880,16 +3194,16 @@
         <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2940,7 +3254,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2952,13 +3266,13 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -2967,16 +3281,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2995,16 +3309,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3042,19 +3356,19 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3066,13 +3380,13 @@
         <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3081,12 +3395,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3106,19 +3420,23 @@
         <v>78</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3166,7 +3484,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3178,38 +3496,38 @@
         <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>78</v>
+        <v>192</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>78</v>
@@ -3218,19 +3536,19 @@
         <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>135</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3280,74 +3598,72 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>78</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3396,39 +3712,39 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>131</v>
+        <v>205</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>78</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3436,7 +3752,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>88</v>
@@ -3448,20 +3764,20 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -3510,10 +3826,10 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>88</v>
@@ -3525,24 +3841,24 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3562,20 +3878,22 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -3642,21 +3960,21 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>78</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3676,19 +3994,23 @@
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -3736,7 +4058,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3751,10 +4073,10 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -3763,7 +4085,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>231</v>
       </c>
@@ -3785,13 +4107,13 @@
         <v>78</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>232</v>
@@ -3799,7 +4121,9 @@
       <c r="M24" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N24" s="2"/>
+      <c r="N24" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -3824,13 +4148,13 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -3863,10 +4187,10 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -3875,12 +4199,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3900,16 +4224,16 @@
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3960,7 +4284,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3972,41 +4296,41 @@
         <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>78</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>78</v>
@@ -4015,16 +4339,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>137</v>
+        <v>250</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4050,13 +4374,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>78</v>
+        <v>253</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4074,75 +4398,71 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -4190,25 +4510,25 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -4217,23 +4537,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -4245,15 +4565,17 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>200</v>
+        <v>134</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -4290,51 +4612,51 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>241</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4345,28 +4667,32 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -4414,13 +4740,13 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>242</v>
+        <v>180</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>78</v>
@@ -4429,19 +4755,3911 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>246</v>
+        <v>181</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>247</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AC43" s="2"/>
+      <c r="AD43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>344</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN63">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI62">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:21:07+00:00</t>
+    <t>2026-04-01T03:34:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Philippines</t>
+    <t>Philippines (the)</t>
   </si>
   <si>
     <t>Description</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:34:09+00:00</t>
+    <t>2026-04-01T03:44:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:44:59+00:00</t>
+    <t>2026-04-06T07:53:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$42</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="285">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-06T07:53:57+00:00</t>
+    <t>2026-04-08T04:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -597,127 +597,6 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>Medication.code.coding.id</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
     <t>Medication.code.text</t>
   </si>
   <si>
@@ -832,27 +711,6 @@
     <t>Medication.form.coding</t>
   </si>
   <si>
-    <t>Medication.form.coding.id</t>
-  </si>
-  <si>
-    <t>Medication.form.coding.extension</t>
-  </si>
-  <si>
-    <t>Medication.form.coding.system</t>
-  </si>
-  <si>
-    <t>Medication.form.coding.version</t>
-  </si>
-  <si>
-    <t>Medication.form.coding.code</t>
-  </si>
-  <si>
-    <t>Medication.form.coding.display</t>
-  </si>
-  <si>
-    <t>Medication.form.coding.userSelected</t>
-  </si>
-  <si>
     <t>Medication.form.text</t>
   </si>
   <si>
@@ -964,48 +822,6 @@
     <t>Medication.ingredient.item[x].coding</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.system</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.system</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.version</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.version</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.display</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.display</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.userSelected</t>
-  </si>
-  <si>
     <t>Medication.ingredient.item[x]:itemCodeableConcept.text</t>
   </si>
   <si>
@@ -1013,6 +829,10 @@
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
   </si>
   <si>
     <t>Active ingredient indicator</t>
@@ -1411,11 +1231,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN63"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="58.71875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.75" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.4140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -3169,7 +2989,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>183</v>
       </c>
@@ -3188,25 +3008,29 @@
         <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>163</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>78</v>
       </c>
@@ -3254,7 +3078,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3266,59 +3090,59 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>78</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>137</v>
+        <v>194</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3344,49 +3168,49 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3397,10 +3221,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3423,20 +3247,16 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3484,7 +3304,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3499,24 +3319,24 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="19" hidden="true">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3530,25 +3350,25 @@
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3574,13 +3394,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -3598,7 +3418,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3613,24 +3433,24 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3644,27 +3464,25 @@
         <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
       </c>
@@ -3712,7 +3530,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3724,38 +3542,38 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>78</v>
@@ -3764,21 +3582,21 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
       </c>
@@ -3814,51 +3632,51 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3869,10 +3687,10 @@
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>78</v>
@@ -3881,19 +3699,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -3942,13 +3760,13 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>78</v>
@@ -3960,21 +3778,21 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="23" hidden="true">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3988,7 +3806,7 @@
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
@@ -4000,16 +3818,16 @@
         <v>163</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4058,7 +3876,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4076,21 +3894,21 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>230</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4107,23 +3925,21 @@
         <v>78</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>222</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4148,13 +3964,13 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -4172,7 +3988,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4190,7 +4006,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4201,10 +4017,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4215,7 +4031,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -4224,18 +4040,20 @@
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4284,13 +4102,13 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>78</v>
@@ -4299,24 +4117,24 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4330,7 +4148,7 @@
         <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>78</v>
@@ -4339,17 +4157,15 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>164</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4374,13 +4190,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>251</v>
+        <v>78</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>252</v>
+        <v>78</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4398,7 +4214,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>166</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4410,38 +4226,38 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>255</v>
+        <v>167</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>256</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
@@ -4453,15 +4269,17 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4510,19 +4328,19 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4539,14 +4357,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>133</v>
+        <v>235</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4559,24 +4377,26 @@
         <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>135</v>
+        <v>236</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="O28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -4612,19 +4432,19 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>173</v>
+        <v>238</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4642,7 +4462,7 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -4651,12 +4471,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4664,34 +4484,32 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>176</v>
+        <v>241</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>179</v>
+        <v>243</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -4728,25 +4546,23 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>180</v>
+        <v>239</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>78</v>
@@ -4755,26 +4571,28 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>181</v>
+        <v>245</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="30" hidden="true">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>78</v>
       </c>
@@ -4786,7 +4604,7 @@
         <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>78</v>
@@ -4795,16 +4613,18 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>164</v>
+        <v>241</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>165</v>
+        <v>242</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -4852,10 +4672,10 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>88</v>
@@ -4864,38 +4684,38 @@
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>78</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
@@ -4907,17 +4727,15 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -4954,31 +4772,31 @@
         <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>78</v>
@@ -4995,21 +4813,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
@@ -5018,23 +4836,21 @@
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5070,51 +4886,51 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5125,10 +4941,10 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>78</v>
@@ -5137,18 +4953,20 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
@@ -5196,13 +5014,13 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>78</v>
@@ -5214,21 +5032,21 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5251,17 +5069,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5310,7 +5130,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5328,21 +5148,21 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5362,20 +5182,20 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>163</v>
+        <v>258</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>209</v>
+        <v>260</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>210</v>
+        <v>261</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5424,7 +5244,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5442,21 +5262,21 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>212</v>
+        <v>262</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5476,23 +5296,19 @@
         <v>78</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5540,7 +5356,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5555,24 +5371,24 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>222</v>
+        <v>267</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5592,23 +5408,19 @@
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -5656,7 +5468,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5671,24 +5483,24 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>230</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5708,16 +5520,16 @@
         <v>78</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5768,7 +5580,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>268</v>
+        <v>166</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5780,13 +5592,13 @@
         <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>272</v>
+        <v>167</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -5804,7 +5616,7 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5823,16 +5635,16 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>274</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>275</v>
+        <v>135</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>276</v>
+        <v>169</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>277</v>
+        <v>137</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5882,7 +5694,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>273</v>
+        <v>173</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5894,13 +5706,13 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>278</v>
+        <v>167</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -5911,42 +5723,46 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>164</v>
+        <v>236</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
       </c>
@@ -5994,25 +5810,25 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6023,21 +5839,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
@@ -6049,17 +5865,15 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>135</v>
+        <v>276</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -6108,75 +5922,71 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>173</v>
+        <v>275</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>78</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>282</v>
+        <v>78</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>280</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6224,2425 +6034,35 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="43" hidden="true">
-      <c r="A43" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AC43" s="2"/>
-      <c r="AD43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="D44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="P44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="48" hidden="true">
-      <c r="A48" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="49" hidden="true">
-      <c r="A49" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="M61" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N61" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>344</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN63">
+  <autoFilter ref="A1:AN42">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8652,7 +6072,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI62">
+  <conditionalFormatting sqref="A2:AI41">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-medication.xlsx
+++ b/dev/StructureDefinition-ph-core-medication.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:01:15+00:00</t>
+    <t>2026-04-13T08:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
